--- a/TelemetrixAI_QA_TestExecution_Report.xlsx
+++ b/TelemetrixAI_QA_TestExecution_Report.xlsx
@@ -259,6 +259,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -284,6 +287,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -309,6 +315,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6276,12 +6285,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Initially blank (DEF-005: Y-axis fields missing Aggregation wrapper). Fix applied and unit-verified against schema, but not re-confirmed visually by the user after the fix.</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>PENDING RE-VERIFICATION</t>
+          <t>User-confirmed via screenshot 2026-09-17: line chart shows real data (latency spike visible), column chart shows real anomaly counts per component (cart/checkout/product-catalog), card shows real value (7.95 error_rate_pct). All 3 visuals genuinely rendering.</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -6306,7 +6315,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>DEF-005 (fixed, unconfirmed visually)</t>
+          <t>DEF-005 (fixed, confirmed)</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6641,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Flag's targeting rule returns 'off' unconditionally on both branches of its if/else (a bug in the OTel Demo's own shipped config, not in this project's code) - flag can never actually activate through normal means</t>
+          <t>Targeting rule bug found and fixed (DEF-003): both if/else branches hardcoded to 'off' were corrected so the 'on' branch now actually fires on product_id match. Flag can now activate - not yet exercised with a real capture (no traffic has been driven at the specific targeted product_id).</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -6662,7 +6671,7 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>DEF-003</t>
+          <t>DEF-003 (config fixed, capture not yet run)</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6986,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Open (third-party/upstream)</t>
+          <t>Fixed (config corrected; real capture against it not yet run)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -6990,7 +6999,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Inspect ~/opentelemetry-demo/opentelemetry-demo/src/flagd/demo.flagd.json -&gt; flags.productCatalogFailure.targeting</t>
@@ -7003,7 +7016,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Workaround, not a code fix: directly edit the targeting rule's branches to 'on'/'off' to make it usable, or use a sidecar fault-injection proxy (e.g., Toxiproxy) as already recommended in FINAL_TERM_CONTENT_DRAFT.md Section 10.</t>
+          <t>Workaround, not a code fix: directly edit the targeting rule's branches to 'on'/'off' to make it usable, or use a sidecar fault-injection proxy (e.g., Toxiproxy) as already recommended in FINAL_TERM_CONTENT_DRAFT.md Section 10. UPDATE 2026-09-17: targeting rule if-branch corrected from 'off' to 'on' directly in the demo flagd config (backup kept). Flag can now genuinely activate on the targeted product_id; a real capture exercising it has not yet been run.</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -7658,6 +7671,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -7745,6 +7760,8 @@
         <v>11</v>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
@@ -7752,6 +7769,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
@@ -7759,6 +7777,41 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
@@ -7766,6 +7819,11 @@
         </is>
       </c>
     </row>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>

--- a/TelemetrixAI_QA_TestExecution_Report.xlsx
+++ b/TelemetrixAI_QA_TestExecution_Report.xlsx
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +160,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -614,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N98"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6070,12 +6076,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>No API key available in this environment - code path implemented and unit-tested, but not exercised live. Not a defect: requires a credential only the account owner can provide.</t>
+          <t>Deliberate decision (2026-09-17): Ollama already provides a real, working AI narrative (see next row), which satisfies the RFP's 'AI must be a core component' requirement. Adding a second live provider was judged not worth the setup for this timeline.</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>DEFERRED (by decision)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -6641,12 +6647,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Targeting rule bug found and fixed (DEF-003): both if/else branches hardcoded to 'off' were corrected so the 'on' branch now actually fires on product_id match. Flag can now activate - not yet exercised with a real capture (no traffic has been driven at the specific targeted product_id).</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Fixed 2026-09-17: targeting rule's if-branch corrected from 'off' to 'on' directly in the demo's flagd config (backup kept at demo.flagd.json.bak). Flag can now genuinely activate. A real capture exercising it has not yet been run (needs live traffic hitting the specific targeted product_id, OLJCESPC7Z).</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>FIXED (capture pending)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -6671,84 +6677,224 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>DEF-003 (config fixed, capture not yet run)</t>
-        </is>
-      </c>
-    </row>
+          <t>DEF-003 (fixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89"/>
+    <row r="90"/>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>TC-M015</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Layer 2 (Azure Monitor)</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Manual / E2E</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Azure Monitor cloud metric sink provisioned</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1. Assess whether an Azure subscription is available
+2. Decide whether to provision a Log Analytics Workspace</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Either a working cloud sink, or an explicit documented decision to skip it</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Deliberate decision (2026-09-17): no Azure subscription available; provisioning one is a real cloud-infrastructure task, not a quick credential add. Prometheus + Jaeger already cover telemetry needs locally.</t>
+        </is>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>DEFERRED (by decision)</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Keerthiga Thirupathi (+ Claude, pair-QA session)</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>TC-M016</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Layer 4 (PySpark)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Automated + Manual verification</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>PySpark local job builds the unified dataset and a component x scenario signal profile</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Java (JDK 17) and PySpark installed</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1. Run spark_processing.py against real collector CSVs
+2. Inspect the written Parquet unified dataset and the printed profile table</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Real p50/p95/p99 + mean signal profile per component x scenario, unified dataset written as Parquet</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Verified: unified dataset (90 real rows) written to unified_dataset/ Parquet; profile table correctly computed for all 4 component x scenario combinations present in the real data</t>
+        </is>
+      </c>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Y (3 pytest cases, 67% coverage)</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Keerthiga Thirupathi (+ Claude, pair-QA session)</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>Total test cases</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>73</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Manual / E2E</t>
+          <t>Total test cases</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Manual / E2E</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Blocked / Pending re-verification</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Blocked / Pending re-verification</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
           <t>Automated coverage (5 core modules)</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7671,8 +7817,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -7760,8 +7904,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
@@ -7769,7 +7911,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
@@ -7777,41 +7918,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
@@ -7819,11 +7925,6 @@
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
